--- a/diseases/d213/2015-2019.xlsx
+++ b/diseases/d213/2015-2019.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20661,7 +20661,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22233,7 +22233,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -23019,7 +23019,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23805,7 +23805,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26163,7 +26163,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27735,7 +27735,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28521,7 +28521,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29307,7 +29307,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30093,7 +30093,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30879,7 +30879,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31665,7 +31665,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32451,7 +32451,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33237,7 +33237,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -34023,7 +34023,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34809,7 +34809,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35595,7 +35595,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -36381,7 +36381,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -37167,7 +37167,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37953,7 +37953,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39525,7 +39525,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -40311,7 +40311,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -41097,7 +41097,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -41883,7 +41883,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -42669,7 +42669,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -43455,7 +43455,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -44241,7 +44241,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -45027,7 +45027,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -45813,7 +45813,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -46599,7 +46599,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -47385,7 +47385,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN239" t="b">

--- a/diseases/d213/2015-2019.xlsx
+++ b/diseases/d213/2015-2019.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24581,7 +24581,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25367,7 +25367,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26153,7 +26153,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26939,7 +26939,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28511,7 +28511,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29297,7 +29297,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30869,7 +30869,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31655,7 +31655,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32441,7 +32441,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33227,7 +33227,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34013,7 +34013,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34799,7 +34799,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35585,7 +35585,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36371,7 +36371,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37157,7 +37157,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37943,7 +37943,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38729,7 +38729,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39515,7 +39515,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40301,7 +40301,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41087,7 +41087,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41873,7 +41873,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42659,7 +42659,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43445,7 +43445,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44231,7 +44231,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45017,7 +45017,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45803,7 +45803,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46589,7 +46589,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47375,7 +47375,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
